--- a/備品管理/備品管理_詳細設計書_検索画面/備品管理_詳細設計書_検索画面.xlsx
+++ b/備品管理/備品管理_詳細設計書_検索画面/備品管理_詳細設計書_検索画面.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://techno08-my.sharepoint.com/personal/naruse-koharu_techno-concier_co_jp/Documents/研修/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3FADA3D9-776A-43D3-B959-B4C1C991EB5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B987E748-BADD-4B5A-BEFE-F4D8610E0078}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="8880" tabRatio="500" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3000" yWindow="3000" windowWidth="17280" windowHeight="8880" tabRatio="500" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="改訂履歴" sheetId="1" r:id="rId1"/>
@@ -2083,6 +2083,9 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2119,9 +2122,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2137,10 +2137,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="3" quotePrefix="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2155,13 +2152,16 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="3" quotePrefix="1" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4008,16 +4008,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" x14ac:dyDescent="0.45">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="79" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
       <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
@@ -4056,22 +4056,22 @@
       </c>
       <c r="AI1" s="6"/>
       <c r="AJ1" s="7"/>
-      <c r="AK1" s="79">
+      <c r="AK1" s="80">
         <v>46125</v>
       </c>
-      <c r="AL1" s="80"/>
-      <c r="AM1" s="80"/>
-      <c r="AN1" s="81"/>
+      <c r="AL1" s="81"/>
+      <c r="AM1" s="81"/>
+      <c r="AN1" s="82"/>
     </row>
     <row r="2" spans="1:40" x14ac:dyDescent="0.45">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
+      <c r="A2" s="79"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
+      <c r="F2" s="79"/>
+      <c r="G2" s="79"/>
+      <c r="H2" s="79"/>
       <c r="I2" s="5" t="s">
         <v>10</v>
       </c>
@@ -4459,16 +4459,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" x14ac:dyDescent="0.45">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="79" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
       <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
@@ -4507,22 +4507,22 @@
       </c>
       <c r="AI1" s="6"/>
       <c r="AJ1" s="7"/>
-      <c r="AK1" s="79">
+      <c r="AK1" s="80">
         <v>46125</v>
       </c>
-      <c r="AL1" s="80"/>
-      <c r="AM1" s="80"/>
-      <c r="AN1" s="81"/>
+      <c r="AL1" s="81"/>
+      <c r="AM1" s="81"/>
+      <c r="AN1" s="82"/>
     </row>
     <row r="2" spans="1:40" x14ac:dyDescent="0.45">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
+      <c r="A2" s="79"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
+      <c r="F2" s="79"/>
+      <c r="G2" s="79"/>
+      <c r="H2" s="79"/>
       <c r="I2" s="5" t="s">
         <v>10</v>
       </c>
@@ -5008,18 +5008,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:47" x14ac:dyDescent="0.2">
-      <c r="A1" s="98" t="s">
+      <c r="A1" s="97" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="98"/>
-      <c r="C1" s="98"/>
-      <c r="D1" s="98"/>
-      <c r="E1" s="98"/>
-      <c r="F1" s="98"/>
-      <c r="G1" s="98"/>
-      <c r="H1" s="98"/>
-      <c r="I1" s="98"/>
-      <c r="J1" s="98"/>
+      <c r="B1" s="97"/>
+      <c r="C1" s="97"/>
+      <c r="D1" s="97"/>
+      <c r="E1" s="97"/>
+      <c r="F1" s="97"/>
+      <c r="G1" s="97"/>
+      <c r="H1" s="97"/>
+      <c r="I1" s="97"/>
+      <c r="J1" s="97"/>
       <c r="K1" s="40" t="s">
         <v>8</v>
       </c>
@@ -5063,24 +5063,24 @@
       </c>
       <c r="AP1" s="41"/>
       <c r="AQ1" s="42"/>
-      <c r="AR1" s="79">
+      <c r="AR1" s="80">
         <v>46126</v>
       </c>
-      <c r="AS1" s="80"/>
-      <c r="AT1" s="80"/>
-      <c r="AU1" s="81"/>
+      <c r="AS1" s="81"/>
+      <c r="AT1" s="81"/>
+      <c r="AU1" s="82"/>
     </row>
     <row r="2" spans="1:47" x14ac:dyDescent="0.2">
-      <c r="A2" s="98"/>
-      <c r="B2" s="98"/>
-      <c r="C2" s="98"/>
-      <c r="D2" s="98"/>
-      <c r="E2" s="98"/>
-      <c r="F2" s="98"/>
-      <c r="G2" s="98"/>
-      <c r="H2" s="98"/>
-      <c r="I2" s="98"/>
-      <c r="J2" s="98"/>
+      <c r="A2" s="97"/>
+      <c r="B2" s="97"/>
+      <c r="C2" s="97"/>
+      <c r="D2" s="97"/>
+      <c r="E2" s="97"/>
+      <c r="F2" s="97"/>
+      <c r="G2" s="97"/>
+      <c r="H2" s="97"/>
+      <c r="I2" s="97"/>
+      <c r="J2" s="97"/>
       <c r="K2" s="40" t="s">
         <v>10</v>
       </c>
@@ -5187,60 +5187,60 @@
       <c r="A5" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="99" t="s">
+      <c r="B5" s="98" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="99"/>
-      <c r="D5" s="99"/>
-      <c r="E5" s="99"/>
-      <c r="F5" s="99"/>
-      <c r="G5" s="99"/>
-      <c r="H5" s="99"/>
-      <c r="I5" s="99"/>
-      <c r="J5" s="99"/>
-      <c r="K5" s="100"/>
-      <c r="L5" s="100"/>
-      <c r="M5" s="100"/>
-      <c r="N5" s="100"/>
-      <c r="O5" s="100"/>
-      <c r="P5" s="100"/>
-      <c r="Q5" s="100"/>
-      <c r="R5" s="100"/>
-      <c r="S5" s="100"/>
-      <c r="T5" s="100"/>
-      <c r="U5" s="100" t="s">
+      <c r="C5" s="98"/>
+      <c r="D5" s="98"/>
+      <c r="E5" s="98"/>
+      <c r="F5" s="98"/>
+      <c r="G5" s="98"/>
+      <c r="H5" s="98"/>
+      <c r="I5" s="98"/>
+      <c r="J5" s="98"/>
+      <c r="K5" s="99"/>
+      <c r="L5" s="99"/>
+      <c r="M5" s="99"/>
+      <c r="N5" s="99"/>
+      <c r="O5" s="99"/>
+      <c r="P5" s="99"/>
+      <c r="Q5" s="99"/>
+      <c r="R5" s="99"/>
+      <c r="S5" s="99"/>
+      <c r="T5" s="99"/>
+      <c r="U5" s="99" t="s">
         <v>23</v>
       </c>
-      <c r="V5" s="100"/>
-      <c r="W5" s="100"/>
-      <c r="X5" s="100"/>
-      <c r="Y5" s="101" t="s">
+      <c r="V5" s="99"/>
+      <c r="W5" s="99"/>
+      <c r="X5" s="99"/>
+      <c r="Y5" s="100" t="s">
         <v>24</v>
       </c>
-      <c r="Z5" s="101"/>
-      <c r="AA5" s="101"/>
-      <c r="AB5" s="101"/>
-      <c r="AC5" s="99" t="s">
+      <c r="Z5" s="100"/>
+      <c r="AA5" s="100"/>
+      <c r="AB5" s="100"/>
+      <c r="AC5" s="98" t="s">
         <v>19</v>
       </c>
-      <c r="AD5" s="99"/>
-      <c r="AE5" s="99"/>
-      <c r="AF5" s="99"/>
-      <c r="AG5" s="99"/>
-      <c r="AH5" s="99"/>
-      <c r="AI5" s="99"/>
-      <c r="AJ5" s="99"/>
-      <c r="AK5" s="99"/>
-      <c r="AL5" s="99"/>
-      <c r="AM5" s="99"/>
-      <c r="AN5" s="99"/>
-      <c r="AO5" s="99"/>
-      <c r="AP5" s="99"/>
-      <c r="AQ5" s="99"/>
-      <c r="AR5" s="99"/>
-      <c r="AS5" s="99"/>
-      <c r="AT5" s="99"/>
-      <c r="AU5" s="99"/>
+      <c r="AD5" s="98"/>
+      <c r="AE5" s="98"/>
+      <c r="AF5" s="98"/>
+      <c r="AG5" s="98"/>
+      <c r="AH5" s="98"/>
+      <c r="AI5" s="98"/>
+      <c r="AJ5" s="98"/>
+      <c r="AK5" s="98"/>
+      <c r="AL5" s="98"/>
+      <c r="AM5" s="98"/>
+      <c r="AN5" s="98"/>
+      <c r="AO5" s="98"/>
+      <c r="AP5" s="98"/>
+      <c r="AQ5" s="98"/>
+      <c r="AR5" s="98"/>
+      <c r="AS5" s="98"/>
+      <c r="AT5" s="98"/>
+      <c r="AU5" s="98"/>
     </row>
     <row r="6" spans="1:47" s="46" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A6" s="51">
@@ -5276,7 +5276,7 @@
       <c r="V6" s="94"/>
       <c r="W6" s="94"/>
       <c r="X6" s="94"/>
-      <c r="Y6" s="102" t="s">
+      <c r="Y6" s="96" t="s">
         <v>66</v>
       </c>
       <c r="Z6" s="95"/>
@@ -5459,9 +5459,9 @@
       <c r="Y9" s="94">
         <v>1</v>
       </c>
-      <c r="Z9" s="96"/>
-      <c r="AA9" s="96"/>
-      <c r="AB9" s="97"/>
+      <c r="Z9" s="101"/>
+      <c r="AA9" s="101"/>
+      <c r="AB9" s="102"/>
       <c r="AC9" s="93"/>
       <c r="AD9" s="93"/>
       <c r="AE9" s="93"/>
@@ -6148,12 +6148,53 @@
     </row>
   </sheetData>
   <mergeCells count="65">
-    <mergeCell ref="B10:J10"/>
-    <mergeCell ref="U10:X10"/>
-    <mergeCell ref="Y10:AB10"/>
-    <mergeCell ref="B11:J11"/>
-    <mergeCell ref="U11:X11"/>
-    <mergeCell ref="Y11:AB11"/>
+    <mergeCell ref="B14:J14"/>
+    <mergeCell ref="U14:X14"/>
+    <mergeCell ref="Y14:AB14"/>
+    <mergeCell ref="B12:J12"/>
+    <mergeCell ref="U12:X12"/>
+    <mergeCell ref="Y12:AB12"/>
+    <mergeCell ref="B13:J13"/>
+    <mergeCell ref="U13:X13"/>
+    <mergeCell ref="Y13:AB13"/>
+    <mergeCell ref="B15:J15"/>
+    <mergeCell ref="U15:X15"/>
+    <mergeCell ref="Y15:AB15"/>
+    <mergeCell ref="AC15:AU15"/>
+    <mergeCell ref="B16:J16"/>
+    <mergeCell ref="U16:X16"/>
+    <mergeCell ref="Y16:AB16"/>
+    <mergeCell ref="AC16:AU16"/>
+    <mergeCell ref="B20:J20"/>
+    <mergeCell ref="U20:X20"/>
+    <mergeCell ref="Y20:AB20"/>
+    <mergeCell ref="AC20:AU20"/>
+    <mergeCell ref="B17:J17"/>
+    <mergeCell ref="U17:X17"/>
+    <mergeCell ref="Y17:AB17"/>
+    <mergeCell ref="AC17:AU17"/>
+    <mergeCell ref="B18:J18"/>
+    <mergeCell ref="U18:X18"/>
+    <mergeCell ref="Y18:AB18"/>
+    <mergeCell ref="AC18:AU18"/>
+    <mergeCell ref="B19:J19"/>
+    <mergeCell ref="U19:X19"/>
+    <mergeCell ref="Y19:AB19"/>
+    <mergeCell ref="AC19:AU19"/>
+    <mergeCell ref="AC13:AU13"/>
+    <mergeCell ref="AC14:AU14"/>
+    <mergeCell ref="Y9:AB9"/>
+    <mergeCell ref="AC9:AU9"/>
+    <mergeCell ref="AC10:AU10"/>
+    <mergeCell ref="AC11:AU11"/>
+    <mergeCell ref="AC12:AU12"/>
+    <mergeCell ref="A1:J2"/>
+    <mergeCell ref="AR1:AU1"/>
+    <mergeCell ref="B5:J5"/>
+    <mergeCell ref="K5:T5"/>
+    <mergeCell ref="U5:X5"/>
+    <mergeCell ref="Y5:AB5"/>
+    <mergeCell ref="AC5:AU5"/>
     <mergeCell ref="B8:J8"/>
     <mergeCell ref="U8:X8"/>
     <mergeCell ref="Y8:AB8"/>
@@ -6166,53 +6207,12 @@
     <mergeCell ref="U7:X7"/>
     <mergeCell ref="Y7:AB7"/>
     <mergeCell ref="AC7:AU7"/>
-    <mergeCell ref="A1:J2"/>
-    <mergeCell ref="AR1:AU1"/>
-    <mergeCell ref="B5:J5"/>
-    <mergeCell ref="K5:T5"/>
-    <mergeCell ref="U5:X5"/>
-    <mergeCell ref="Y5:AB5"/>
-    <mergeCell ref="AC5:AU5"/>
-    <mergeCell ref="AC13:AU13"/>
-    <mergeCell ref="AC14:AU14"/>
-    <mergeCell ref="Y9:AB9"/>
-    <mergeCell ref="AC9:AU9"/>
-    <mergeCell ref="AC10:AU10"/>
-    <mergeCell ref="AC11:AU11"/>
-    <mergeCell ref="B20:J20"/>
-    <mergeCell ref="U20:X20"/>
-    <mergeCell ref="Y20:AB20"/>
-    <mergeCell ref="AC20:AU20"/>
-    <mergeCell ref="B17:J17"/>
-    <mergeCell ref="U17:X17"/>
-    <mergeCell ref="Y17:AB17"/>
-    <mergeCell ref="AC17:AU17"/>
-    <mergeCell ref="B18:J18"/>
-    <mergeCell ref="U18:X18"/>
-    <mergeCell ref="Y18:AB18"/>
-    <mergeCell ref="AC18:AU18"/>
-    <mergeCell ref="AC12:AU12"/>
-    <mergeCell ref="B19:J19"/>
-    <mergeCell ref="U19:X19"/>
-    <mergeCell ref="Y19:AB19"/>
-    <mergeCell ref="AC19:AU19"/>
-    <mergeCell ref="B15:J15"/>
-    <mergeCell ref="U15:X15"/>
-    <mergeCell ref="Y15:AB15"/>
-    <mergeCell ref="AC15:AU15"/>
-    <mergeCell ref="B16:J16"/>
-    <mergeCell ref="U16:X16"/>
-    <mergeCell ref="Y16:AB16"/>
-    <mergeCell ref="AC16:AU16"/>
-    <mergeCell ref="B12:J12"/>
-    <mergeCell ref="U12:X12"/>
-    <mergeCell ref="Y12:AB12"/>
-    <mergeCell ref="B13:J13"/>
-    <mergeCell ref="U13:X13"/>
-    <mergeCell ref="Y13:AB13"/>
-    <mergeCell ref="B14:J14"/>
-    <mergeCell ref="U14:X14"/>
-    <mergeCell ref="Y14:AB14"/>
+    <mergeCell ref="B10:J10"/>
+    <mergeCell ref="U10:X10"/>
+    <mergeCell ref="Y10:AB10"/>
+    <mergeCell ref="B11:J11"/>
+    <mergeCell ref="U11:X11"/>
+    <mergeCell ref="Y11:AB11"/>
   </mergeCells>
   <phoneticPr fontId="7"/>
   <pageMargins left="0.196527777777778" right="0.196527777777778" top="0.39374999999999999" bottom="0.39374999999999999" header="0.51180555555555496" footer="0.31527777777777799"/>
@@ -6232,16 +6232,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" x14ac:dyDescent="0.45">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="79" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
       <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
@@ -6280,22 +6280,22 @@
       </c>
       <c r="AI1" s="6"/>
       <c r="AJ1" s="7"/>
-      <c r="AK1" s="79">
+      <c r="AK1" s="80">
         <v>46126</v>
       </c>
-      <c r="AL1" s="80"/>
-      <c r="AM1" s="80"/>
-      <c r="AN1" s="81"/>
+      <c r="AL1" s="81"/>
+      <c r="AM1" s="81"/>
+      <c r="AN1" s="82"/>
     </row>
     <row r="2" spans="1:40" x14ac:dyDescent="0.45">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
+      <c r="A2" s="79"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
+      <c r="F2" s="79"/>
+      <c r="G2" s="79"/>
+      <c r="H2" s="79"/>
       <c r="I2" s="5" t="s">
         <v>10</v>
       </c>
@@ -6441,10 +6441,10 @@
       <c r="AN5" s="7"/>
     </row>
     <row r="6" spans="1:40" x14ac:dyDescent="0.45">
-      <c r="A6" s="104" t="s">
+      <c r="A6" s="103" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="104"/>
+      <c r="B6" s="103"/>
       <c r="C6" s="17" t="s">
         <v>133</v>
       </c>
@@ -6487,10 +6487,10 @@
       <c r="AN6" s="12"/>
     </row>
     <row r="7" spans="1:40" x14ac:dyDescent="0.45">
-      <c r="A7" s="104">
+      <c r="A7" s="103">
         <v>1</v>
       </c>
-      <c r="B7" s="104"/>
+      <c r="B7" s="103"/>
       <c r="C7" s="64"/>
       <c r="D7" s="10" t="s">
         <v>134</v>
@@ -6508,14 +6508,14 @@
       <c r="M7" s="11"/>
       <c r="N7" s="11"/>
       <c r="O7" s="12"/>
-      <c r="P7" s="104" t="s">
+      <c r="P7" s="103" t="s">
         <v>69</v>
       </c>
-      <c r="Q7" s="104"/>
-      <c r="R7" s="104">
+      <c r="Q7" s="103"/>
+      <c r="R7" s="103">
         <v>10</v>
       </c>
-      <c r="S7" s="104"/>
+      <c r="S7" s="103"/>
       <c r="T7" s="10" t="s">
         <v>137</v>
       </c>
@@ -6541,10 +6541,10 @@
       <c r="AN7" s="12"/>
     </row>
     <row r="8" spans="1:40" x14ac:dyDescent="0.45">
-      <c r="A8" s="104" t="s">
+      <c r="A8" s="103" t="s">
         <v>70</v>
       </c>
-      <c r="B8" s="104"/>
+      <c r="B8" s="103"/>
       <c r="C8" s="20" t="s">
         <v>136</v>
       </c>
@@ -6587,10 +6587,10 @@
       <c r="AN8" s="12"/>
     </row>
     <row r="9" spans="1:40" x14ac:dyDescent="0.45">
-      <c r="A9" s="104">
+      <c r="A9" s="103">
         <v>2</v>
       </c>
-      <c r="B9" s="104"/>
+      <c r="B9" s="103"/>
       <c r="C9" s="30"/>
       <c r="D9" s="10" t="s">
         <v>138</v>
@@ -6608,14 +6608,14 @@
       <c r="M9" s="11"/>
       <c r="N9" s="11"/>
       <c r="O9" s="12"/>
-      <c r="P9" s="104" t="s">
+      <c r="P9" s="103" t="s">
         <v>69</v>
       </c>
-      <c r="Q9" s="104"/>
-      <c r="R9" s="104">
+      <c r="Q9" s="103"/>
+      <c r="R9" s="103">
         <v>30</v>
       </c>
-      <c r="S9" s="104"/>
+      <c r="S9" s="103"/>
       <c r="T9" s="10" t="s">
         <v>135</v>
       </c>
@@ -6641,10 +6641,10 @@
       <c r="AN9" s="12"/>
     </row>
     <row r="10" spans="1:40" x14ac:dyDescent="0.45">
-      <c r="A10" s="104" t="s">
+      <c r="A10" s="103" t="s">
         <v>70</v>
       </c>
-      <c r="B10" s="104"/>
+      <c r="B10" s="103"/>
       <c r="C10" s="17" t="s">
         <v>139</v>
       </c>
@@ -6687,10 +6687,10 @@
       <c r="AN10" s="12"/>
     </row>
     <row r="11" spans="1:40" x14ac:dyDescent="0.45">
-      <c r="A11" s="104">
+      <c r="A11" s="103">
         <v>3</v>
       </c>
-      <c r="B11" s="104"/>
+      <c r="B11" s="103"/>
       <c r="C11" s="20"/>
       <c r="D11" s="10" t="s">
         <v>140</v>
@@ -6708,14 +6708,14 @@
       <c r="M11" s="11"/>
       <c r="N11" s="11"/>
       <c r="O11" s="12"/>
-      <c r="P11" s="104" t="s">
+      <c r="P11" s="103" t="s">
         <v>69</v>
       </c>
-      <c r="Q11" s="104"/>
-      <c r="R11" s="104" t="s">
+      <c r="Q11" s="103"/>
+      <c r="R11" s="103" t="s">
         <v>6</v>
       </c>
-      <c r="S11" s="104"/>
+      <c r="S11" s="103"/>
       <c r="T11" s="11" t="s">
         <v>159</v>
       </c>
@@ -6741,10 +6741,10 @@
       <c r="AN11" s="12"/>
     </row>
     <row r="12" spans="1:40" x14ac:dyDescent="0.45">
-      <c r="A12" s="104" t="s">
+      <c r="A12" s="103" t="s">
         <v>70</v>
       </c>
-      <c r="B12" s="104"/>
+      <c r="B12" s="103"/>
       <c r="C12" s="17" t="s">
         <v>142</v>
       </c>
@@ -6787,10 +6787,10 @@
       <c r="AN12" s="12"/>
     </row>
     <row r="13" spans="1:40" x14ac:dyDescent="0.45">
-      <c r="A13" s="104">
+      <c r="A13" s="103">
         <v>4</v>
       </c>
-      <c r="B13" s="104"/>
+      <c r="B13" s="103"/>
       <c r="C13" s="30"/>
       <c r="D13" s="10" t="s">
         <v>143</v>
@@ -6841,10 +6841,10 @@
       <c r="AN13" s="12"/>
     </row>
     <row r="14" spans="1:40" x14ac:dyDescent="0.45">
-      <c r="A14" s="104">
+      <c r="A14" s="103">
         <v>5</v>
       </c>
-      <c r="B14" s="104"/>
+      <c r="B14" s="103"/>
       <c r="C14" s="64"/>
       <c r="D14" s="10" t="s">
         <v>144</v>
@@ -6862,14 +6862,14 @@
       <c r="M14" s="11"/>
       <c r="N14" s="11"/>
       <c r="O14" s="12"/>
-      <c r="P14" s="104" t="s">
+      <c r="P14" s="103" t="s">
         <v>69</v>
       </c>
-      <c r="Q14" s="104"/>
-      <c r="R14" s="104" t="s">
+      <c r="Q14" s="103"/>
+      <c r="R14" s="103" t="s">
         <v>6</v>
       </c>
-      <c r="S14" s="104"/>
+      <c r="S14" s="103"/>
       <c r="T14" s="23"/>
       <c r="U14" s="23"/>
       <c r="V14" s="23"/>
@@ -6893,10 +6893,10 @@
       <c r="AN14" s="23"/>
     </row>
     <row r="15" spans="1:40" x14ac:dyDescent="0.45">
-      <c r="A15" s="104" t="s">
+      <c r="A15" s="103" t="s">
         <v>70</v>
       </c>
-      <c r="B15" s="104"/>
+      <c r="B15" s="103"/>
       <c r="C15" s="20" t="s">
         <v>146</v>
       </c>
@@ -6939,10 +6939,10 @@
       <c r="AN15" s="23"/>
     </row>
     <row r="16" spans="1:40" x14ac:dyDescent="0.45">
-      <c r="A16" s="104">
+      <c r="A16" s="103">
         <v>6</v>
       </c>
-      <c r="B16" s="104"/>
+      <c r="B16" s="103"/>
       <c r="C16" s="30"/>
       <c r="D16" s="10" t="s">
         <v>147</v>
@@ -6960,14 +6960,14 @@
       <c r="M16" s="11"/>
       <c r="N16" s="11"/>
       <c r="O16" s="12"/>
-      <c r="P16" s="104" t="s">
+      <c r="P16" s="103" t="s">
         <v>70</v>
       </c>
-      <c r="Q16" s="104"/>
-      <c r="R16" s="104" t="s">
+      <c r="Q16" s="103"/>
+      <c r="R16" s="103" t="s">
         <v>6</v>
       </c>
-      <c r="S16" s="104"/>
+      <c r="S16" s="103"/>
       <c r="T16" s="23"/>
       <c r="U16" s="23"/>
       <c r="V16" s="23"/>
@@ -6991,10 +6991,10 @@
       <c r="AN16" s="23"/>
     </row>
     <row r="17" spans="1:40" x14ac:dyDescent="0.45">
-      <c r="A17" s="104">
+      <c r="A17" s="103">
         <v>7</v>
       </c>
-      <c r="B17" s="104"/>
+      <c r="B17" s="103"/>
       <c r="C17" s="64"/>
       <c r="D17" s="10" t="s">
         <v>72</v>
@@ -7012,14 +7012,14 @@
       <c r="M17" s="11"/>
       <c r="N17" s="11"/>
       <c r="O17" s="12"/>
-      <c r="P17" s="104" t="s">
+      <c r="P17" s="103" t="s">
         <v>78</v>
       </c>
-      <c r="Q17" s="104"/>
-      <c r="R17" s="104" t="s">
+      <c r="Q17" s="103"/>
+      <c r="R17" s="103" t="s">
         <v>6</v>
       </c>
-      <c r="S17" s="104"/>
+      <c r="S17" s="103"/>
       <c r="T17" s="23"/>
       <c r="U17" s="23"/>
       <c r="V17" s="23"/>
@@ -7043,10 +7043,10 @@
       <c r="AN17" s="23"/>
     </row>
     <row r="18" spans="1:40" x14ac:dyDescent="0.45">
-      <c r="A18" s="104" t="s">
+      <c r="A18" s="103" t="s">
         <v>70</v>
       </c>
-      <c r="B18" s="104"/>
+      <c r="B18" s="103"/>
       <c r="C18" s="20" t="s">
         <v>149</v>
       </c>
@@ -7089,10 +7089,10 @@
       <c r="AN18" s="23"/>
     </row>
     <row r="19" spans="1:40" x14ac:dyDescent="0.45">
-      <c r="A19" s="104">
+      <c r="A19" s="103">
         <v>8</v>
       </c>
-      <c r="B19" s="104"/>
+      <c r="B19" s="103"/>
       <c r="C19" s="20"/>
       <c r="D19" s="10" t="s">
         <v>55</v>
@@ -7133,10 +7133,10 @@
       <c r="AN19" s="23"/>
     </row>
     <row r="20" spans="1:40" x14ac:dyDescent="0.45">
-      <c r="A20" s="104">
+      <c r="A20" s="103">
         <v>9</v>
       </c>
-      <c r="B20" s="104"/>
+      <c r="B20" s="103"/>
       <c r="C20" s="20"/>
       <c r="D20" s="10" t="s">
         <v>56</v>
@@ -7154,14 +7154,14 @@
       <c r="M20" s="11"/>
       <c r="N20" s="11"/>
       <c r="O20" s="12"/>
-      <c r="P20" s="104" t="s">
+      <c r="P20" s="103" t="s">
         <v>78</v>
       </c>
-      <c r="Q20" s="104"/>
-      <c r="R20" s="104">
+      <c r="Q20" s="103"/>
+      <c r="R20" s="103">
         <v>30</v>
       </c>
-      <c r="S20" s="104"/>
+      <c r="S20" s="103"/>
       <c r="T20" s="23" t="s">
         <v>135</v>
       </c>
@@ -7187,10 +7187,10 @@
       <c r="AN20" s="23"/>
     </row>
     <row r="21" spans="1:40" x14ac:dyDescent="0.45">
-      <c r="A21" s="104">
+      <c r="A21" s="103">
         <v>10</v>
       </c>
-      <c r="B21" s="104"/>
+      <c r="B21" s="103"/>
       <c r="C21" s="20"/>
       <c r="D21" s="10" t="s">
         <v>57</v>
@@ -7239,10 +7239,10 @@
       <c r="AN21" s="23"/>
     </row>
     <row r="22" spans="1:40" x14ac:dyDescent="0.45">
-      <c r="A22" s="103">
+      <c r="A22" s="104">
         <v>11</v>
       </c>
-      <c r="B22" s="103"/>
+      <c r="B22" s="104"/>
       <c r="C22" s="20"/>
       <c r="D22" s="10" t="s">
         <v>112</v>
@@ -7293,10 +7293,10 @@
       <c r="AN22" s="12"/>
     </row>
     <row r="23" spans="1:40" x14ac:dyDescent="0.45">
-      <c r="A23" s="103">
+      <c r="A23" s="104">
         <v>12</v>
       </c>
-      <c r="B23" s="103"/>
+      <c r="B23" s="104"/>
       <c r="C23" s="20"/>
       <c r="D23" s="10" t="s">
         <v>72</v>
@@ -7325,6 +7325,44 @@
     </row>
   </sheetData>
   <mergeCells count="54">
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="P23:Q23"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="R18:S18"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="P18:Q18"/>
+    <mergeCell ref="P20:Q20"/>
+    <mergeCell ref="P21:Q21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="P22:Q22"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="P8:Q8"/>
+    <mergeCell ref="R8:S8"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="P12:Q12"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="P10:Q10"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="P11:Q11"/>
+    <mergeCell ref="R11:S11"/>
+    <mergeCell ref="P9:Q9"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="AK1:AN1"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="P7:Q7"/>
+    <mergeCell ref="R7:S7"/>
+    <mergeCell ref="A1:H2"/>
     <mergeCell ref="P19:Q19"/>
     <mergeCell ref="R19:S19"/>
     <mergeCell ref="A16:B16"/>
@@ -7341,44 +7379,6 @@
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="P13:Q13"/>
     <mergeCell ref="R13:S13"/>
-    <mergeCell ref="AK1:AN1"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="P7:Q7"/>
-    <mergeCell ref="R7:S7"/>
-    <mergeCell ref="A1:H2"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="P8:Q8"/>
-    <mergeCell ref="R8:S8"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="P12:Q12"/>
-    <mergeCell ref="R12:S12"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="P10:Q10"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="P11:Q11"/>
-    <mergeCell ref="R11:S11"/>
-    <mergeCell ref="P9:Q9"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="P23:Q23"/>
-    <mergeCell ref="R23:S23"/>
-    <mergeCell ref="R18:S18"/>
-    <mergeCell ref="R20:S20"/>
-    <mergeCell ref="R21:S21"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="P18:Q18"/>
-    <mergeCell ref="P20:Q20"/>
-    <mergeCell ref="P21:Q21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="P22:Q22"/>
-    <mergeCell ref="R22:S22"/>
   </mergeCells>
   <phoneticPr fontId="7"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.39370078740157483" bottom="0.39370078740157483" header="0.51181102362204722" footer="0.51181102362204722"/>
@@ -7402,16 +7402,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" x14ac:dyDescent="0.45">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="79" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
       <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
@@ -7450,22 +7450,22 @@
       </c>
       <c r="AI1" s="6"/>
       <c r="AJ1" s="7"/>
-      <c r="AK1" s="79">
+      <c r="AK1" s="80">
         <v>46125</v>
       </c>
-      <c r="AL1" s="80"/>
-      <c r="AM1" s="80"/>
-      <c r="AN1" s="81"/>
+      <c r="AL1" s="81"/>
+      <c r="AM1" s="81"/>
+      <c r="AN1" s="82"/>
     </row>
     <row r="2" spans="1:40" x14ac:dyDescent="0.45">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
+      <c r="A2" s="79"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
+      <c r="F2" s="79"/>
+      <c r="G2" s="79"/>
+      <c r="H2" s="79"/>
       <c r="I2" s="5" t="s">
         <v>10</v>
       </c>
@@ -7657,10 +7657,10 @@
       <c r="AN6" s="19"/>
     </row>
     <row r="7" spans="1:40" x14ac:dyDescent="0.45">
-      <c r="A7" s="104">
+      <c r="A7" s="103">
         <v>2</v>
       </c>
-      <c r="B7" s="104"/>
+      <c r="B7" s="103"/>
       <c r="C7" s="17" t="s">
         <v>147</v>
       </c>
@@ -7731,16 +7731,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" x14ac:dyDescent="0.45">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="79" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
       <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
@@ -7779,22 +7779,22 @@
       </c>
       <c r="AI1" s="6"/>
       <c r="AJ1" s="7"/>
-      <c r="AK1" s="79">
+      <c r="AK1" s="80">
         <v>46126</v>
       </c>
-      <c r="AL1" s="80"/>
-      <c r="AM1" s="80"/>
-      <c r="AN1" s="81"/>
+      <c r="AL1" s="81"/>
+      <c r="AM1" s="81"/>
+      <c r="AN1" s="82"/>
     </row>
     <row r="2" spans="1:40" x14ac:dyDescent="0.45">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
+      <c r="A2" s="79"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
+      <c r="F2" s="79"/>
+      <c r="G2" s="79"/>
+      <c r="H2" s="79"/>
       <c r="I2" s="5" t="s">
         <v>10</v>
       </c>
@@ -8041,16 +8041,16 @@
       <c r="AN16" s="21"/>
     </row>
     <row r="17" spans="1:1025" x14ac:dyDescent="0.45">
-      <c r="B17" s="82" t="s">
+      <c r="B17" s="83" t="s">
         <v>161</v>
       </c>
-      <c r="C17" s="82"/>
-      <c r="D17" s="82"/>
-      <c r="E17" s="82"/>
-      <c r="F17" s="82"/>
-      <c r="G17" s="82"/>
-      <c r="H17" s="82"/>
-      <c r="I17" s="83"/>
+      <c r="C17" s="83"/>
+      <c r="D17" s="83"/>
+      <c r="E17" s="83"/>
+      <c r="F17" s="83"/>
+      <c r="G17" s="83"/>
+      <c r="H17" s="83"/>
+      <c r="I17" s="84"/>
       <c r="J17" s="73"/>
       <c r="K17" s="62" t="s">
         <v>163</v>
@@ -10197,17 +10197,17 @@
     </row>
     <row r="23" spans="1:1025" x14ac:dyDescent="0.45">
       <c r="A23"/>
-      <c r="B23" s="84" t="s">
+      <c r="B23" s="85" t="s">
         <v>169</v>
       </c>
-      <c r="C23" s="85"/>
-      <c r="D23" s="85"/>
-      <c r="E23" s="85"/>
-      <c r="F23" s="85"/>
-      <c r="G23" s="85"/>
-      <c r="H23" s="85"/>
-      <c r="I23" s="85"/>
-      <c r="J23" s="86"/>
+      <c r="C23" s="86"/>
+      <c r="D23" s="86"/>
+      <c r="E23" s="86"/>
+      <c r="F23" s="86"/>
+      <c r="G23" s="86"/>
+      <c r="H23" s="86"/>
+      <c r="I23" s="86"/>
+      <c r="J23" s="87"/>
       <c r="K23" s="18" t="s">
         <v>171</v>
       </c>
@@ -11227,15 +11227,15 @@
     </row>
     <row r="24" spans="1:1025" x14ac:dyDescent="0.45">
       <c r="A24"/>
-      <c r="B24" s="87"/>
-      <c r="C24" s="88"/>
-      <c r="D24" s="88"/>
-      <c r="E24" s="88"/>
-      <c r="F24" s="88"/>
-      <c r="G24" s="88"/>
-      <c r="H24" s="88"/>
-      <c r="I24" s="88"/>
-      <c r="J24" s="89"/>
+      <c r="B24" s="88"/>
+      <c r="C24" s="89"/>
+      <c r="D24" s="89"/>
+      <c r="E24" s="89"/>
+      <c r="F24" s="89"/>
+      <c r="G24" s="89"/>
+      <c r="H24" s="89"/>
+      <c r="I24" s="89"/>
+      <c r="J24" s="90"/>
       <c r="K24"/>
       <c r="L24"/>
       <c r="M24"/>
@@ -12253,17 +12253,17 @@
     </row>
     <row r="25" spans="1:1025" x14ac:dyDescent="0.45">
       <c r="A25"/>
-      <c r="B25" s="84" t="s">
+      <c r="B25" s="85" t="s">
         <v>170</v>
       </c>
-      <c r="C25" s="85"/>
-      <c r="D25" s="85"/>
-      <c r="E25" s="85"/>
-      <c r="F25" s="85"/>
-      <c r="G25" s="85"/>
-      <c r="H25" s="85"/>
-      <c r="I25" s="85"/>
-      <c r="J25" s="86"/>
+      <c r="C25" s="86"/>
+      <c r="D25" s="86"/>
+      <c r="E25" s="86"/>
+      <c r="F25" s="86"/>
+      <c r="G25" s="86"/>
+      <c r="H25" s="86"/>
+      <c r="I25" s="86"/>
+      <c r="J25" s="87"/>
       <c r="K25"/>
       <c r="L25"/>
       <c r="M25"/>
@@ -13280,15 +13280,15 @@
       <c r="AMK25"/>
     </row>
     <row r="26" spans="1:1025" x14ac:dyDescent="0.45">
-      <c r="B26" s="87"/>
-      <c r="C26" s="88"/>
-      <c r="D26" s="88"/>
-      <c r="E26" s="88"/>
-      <c r="F26" s="88"/>
-      <c r="G26" s="88"/>
-      <c r="H26" s="88"/>
-      <c r="I26" s="88"/>
-      <c r="J26" s="89"/>
+      <c r="B26" s="88"/>
+      <c r="C26" s="89"/>
+      <c r="D26" s="89"/>
+      <c r="E26" s="89"/>
+      <c r="F26" s="89"/>
+      <c r="G26" s="89"/>
+      <c r="H26" s="89"/>
+      <c r="I26" s="89"/>
+      <c r="J26" s="90"/>
       <c r="K26" s="23"/>
       <c r="L26" s="23"/>
       <c r="M26" s="23"/>
@@ -13469,65 +13469,65 @@
       </c>
     </row>
     <row r="44" spans="1:40" x14ac:dyDescent="0.45">
-      <c r="C44" s="90" t="s">
+      <c r="C44" s="78" t="s">
         <v>210</v>
       </c>
-      <c r="D44" s="90"/>
-      <c r="E44" s="90"/>
-      <c r="F44" s="90"/>
-      <c r="G44" s="90"/>
-      <c r="H44" s="90"/>
-      <c r="I44" s="90"/>
-      <c r="J44" s="90"/>
-      <c r="K44" s="90"/>
-      <c r="L44" s="90"/>
-      <c r="M44" s="90"/>
-      <c r="N44" s="90"/>
-      <c r="O44" s="90"/>
-      <c r="P44" s="90"/>
-      <c r="Q44" s="90"/>
-      <c r="R44" s="90"/>
-      <c r="S44" s="90"/>
-      <c r="T44" s="90"/>
-      <c r="U44" s="90"/>
-      <c r="V44" s="90"/>
-      <c r="W44" s="90"/>
-      <c r="X44" s="90"/>
-      <c r="Y44" s="90"/>
-      <c r="Z44" s="90"/>
-      <c r="AA44" s="90"/>
-      <c r="AB44" s="90"/>
-      <c r="AC44" s="90"/>
+      <c r="D44" s="78"/>
+      <c r="E44" s="78"/>
+      <c r="F44" s="78"/>
+      <c r="G44" s="78"/>
+      <c r="H44" s="78"/>
+      <c r="I44" s="78"/>
+      <c r="J44" s="78"/>
+      <c r="K44" s="78"/>
+      <c r="L44" s="78"/>
+      <c r="M44" s="78"/>
+      <c r="N44" s="78"/>
+      <c r="O44" s="78"/>
+      <c r="P44" s="78"/>
+      <c r="Q44" s="78"/>
+      <c r="R44" s="78"/>
+      <c r="S44" s="78"/>
+      <c r="T44" s="78"/>
+      <c r="U44" s="78"/>
+      <c r="V44" s="78"/>
+      <c r="W44" s="78"/>
+      <c r="X44" s="78"/>
+      <c r="Y44" s="78"/>
+      <c r="Z44" s="78"/>
+      <c r="AA44" s="78"/>
+      <c r="AB44" s="78"/>
+      <c r="AC44" s="78"/>
       <c r="AN44" s="21"/>
     </row>
     <row r="45" spans="1:40" x14ac:dyDescent="0.45">
-      <c r="C45" s="90"/>
-      <c r="D45" s="90"/>
-      <c r="E45" s="90"/>
-      <c r="F45" s="90"/>
-      <c r="G45" s="90"/>
-      <c r="H45" s="90"/>
-      <c r="I45" s="90"/>
-      <c r="J45" s="90"/>
-      <c r="K45" s="90"/>
-      <c r="L45" s="90"/>
-      <c r="M45" s="90"/>
-      <c r="N45" s="90"/>
-      <c r="O45" s="90"/>
-      <c r="P45" s="90"/>
-      <c r="Q45" s="90"/>
-      <c r="R45" s="90"/>
-      <c r="S45" s="90"/>
-      <c r="T45" s="90"/>
-      <c r="U45" s="90"/>
-      <c r="V45" s="90"/>
-      <c r="W45" s="90"/>
-      <c r="X45" s="90"/>
-      <c r="Y45" s="90"/>
-      <c r="Z45" s="90"/>
-      <c r="AA45" s="90"/>
-      <c r="AB45" s="90"/>
-      <c r="AC45" s="90"/>
+      <c r="C45" s="78"/>
+      <c r="D45" s="78"/>
+      <c r="E45" s="78"/>
+      <c r="F45" s="78"/>
+      <c r="G45" s="78"/>
+      <c r="H45" s="78"/>
+      <c r="I45" s="78"/>
+      <c r="J45" s="78"/>
+      <c r="K45" s="78"/>
+      <c r="L45" s="78"/>
+      <c r="M45" s="78"/>
+      <c r="N45" s="78"/>
+      <c r="O45" s="78"/>
+      <c r="P45" s="78"/>
+      <c r="Q45" s="78"/>
+      <c r="R45" s="78"/>
+      <c r="S45" s="78"/>
+      <c r="T45" s="78"/>
+      <c r="U45" s="78"/>
+      <c r="V45" s="78"/>
+      <c r="W45" s="78"/>
+      <c r="X45" s="78"/>
+      <c r="Y45" s="78"/>
+      <c r="Z45" s="78"/>
+      <c r="AA45" s="78"/>
+      <c r="AB45" s="78"/>
+      <c r="AC45" s="78"/>
       <c r="AN45" s="21"/>
     </row>
     <row r="46" spans="1:40" x14ac:dyDescent="0.45">
@@ -13651,16 +13651,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1025" x14ac:dyDescent="0.45">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="79" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
       <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
@@ -13699,22 +13699,22 @@
       </c>
       <c r="AI1" s="6"/>
       <c r="AJ1" s="7"/>
-      <c r="AK1" s="79">
+      <c r="AK1" s="80">
         <v>46126</v>
       </c>
-      <c r="AL1" s="80"/>
-      <c r="AM1" s="80"/>
-      <c r="AN1" s="81"/>
+      <c r="AL1" s="81"/>
+      <c r="AM1" s="81"/>
+      <c r="AN1" s="82"/>
     </row>
     <row r="2" spans="1:1025" x14ac:dyDescent="0.45">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
+      <c r="A2" s="79"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
+      <c r="F2" s="79"/>
+      <c r="G2" s="79"/>
+      <c r="H2" s="79"/>
       <c r="I2" s="5" t="s">
         <v>10</v>
       </c>
@@ -31366,20 +31366,20 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="7e7b61e0-3ed5-4e6c-b84b-62be7aa80073" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="7e7b61e0-3ed5-4e6c-b84b-62be7aa80073" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -31557,25 +31557,25 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3D22769B-A213-4965-A373-49CE4994CBF5}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0BA037F7-92E2-4191-8611-939683B19005}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="7e7b61e0-3ed5-4e6c-b84b-62be7aa80073"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0BA037F7-92E2-4191-8611-939683B19005}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3D22769B-A213-4965-A373-49CE4994CBF5}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="7e7b61e0-3ed5-4e6c-b84b-62be7aa80073"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
